--- a/experiment_results/wedos_grid/rtt_bursts_S2_atk1pct_wu500000_stage1b_confirm_rep3.xlsx
+++ b/experiment_results/wedos_grid/rtt_bursts_S2_atk1pct_wu500000_stage1b_confirm_rep3.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>17283</t>
+          <t>10252</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12774</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>705</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5819</t>
+          <t>410</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>14365</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1517,12 +1517,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
